--- a/info/Bewertung.xlsx
+++ b/info/Bewertung.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05_GIT\JuMa_Tir\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C52337-9F26-4834-A3B6-2448828534C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E03F50-6104-4CE3-8A9B-4145DD162B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-2880" windowWidth="30936" windowHeight="16776" xr2:uid="{AFEFCC93-C23D-44FC-ACFD-BDB8AA63CF66}"/>
+    <workbookView xWindow="53652" yWindow="-2880" windowWidth="30936" windowHeight="16776" xr2:uid="{AFEFCC93-C23D-44FC-ACFD-BDB8AA63CF66}"/>
   </bookViews>
   <sheets>
     <sheet name="Stationen" sheetId="1" r:id="rId1"/>
@@ -288,7 +288,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E742889C-8821-4005-9075-3A6DDB05D360}" name="Tabelle1" displayName="Tabelle1" ref="A1:M51" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:M51" xr:uid="{E742889C-8821-4005-9075-3A6DDB05D360}"/>
+  <autoFilter ref="A1:M51" xr:uid="{E742889C-8821-4005-9075-3A6DDB05D360}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Testfragen"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{6C5AE5F5-F82C-46DD-807D-0F5BAF0B4415}" name="Station-Nr" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{7BA1FAE7-66DA-43CA-8533-7F7E0E739CAB}" name="Station"/>
@@ -660,7 +666,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -692,7 +698,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -727,7 +733,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -762,7 +768,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -797,7 +803,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -832,7 +838,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -864,7 +870,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -899,7 +905,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -934,7 +940,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -966,7 +972,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1307,7 +1313,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -1339,7 +1345,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -1374,7 +1380,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -1409,7 +1415,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -1444,7 +1450,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -1479,7 +1485,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -1511,7 +1517,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -1546,7 +1552,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -1581,7 +1587,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -1616,7 +1622,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -1654,7 +1660,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -1686,7 +1692,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -1718,7 +1724,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -1753,7 +1759,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -1788,7 +1794,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -1823,7 +1829,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -1858,7 +1864,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -1890,7 +1896,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -1922,7 +1928,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -1954,7 +1960,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -1986,7 +1992,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -2021,7 +2027,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>4</v>
       </c>
@@ -2053,7 +2059,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>4</v>
       </c>
@@ -2088,7 +2094,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>4</v>
       </c>
@@ -2120,7 +2126,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>4</v>
       </c>
@@ -2152,7 +2158,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>4</v>
       </c>
@@ -2184,7 +2190,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>4</v>
       </c>
@@ -2216,7 +2222,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>4</v>
       </c>
@@ -2248,7 +2254,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>4</v>
       </c>
@@ -2280,7 +2286,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>4</v>
       </c>
@@ -2318,7 +2324,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>4</v>
       </c>

--- a/info/Bewertung.xlsx
+++ b/info/Bewertung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05_GIT\JuMa_Tir\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E03F50-6104-4CE3-8A9B-4145DD162B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A97A90-2113-488D-A88F-C72A7E5C60B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="53652" yWindow="-2880" windowWidth="30936" windowHeight="16776" xr2:uid="{AFEFCC93-C23D-44FC-ACFD-BDB8AA63CF66}"/>
   </bookViews>
@@ -291,7 +291,7 @@
   <autoFilter ref="A1:M51" xr:uid="{E742889C-8821-4005-9075-3A6DDB05D360}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Testfragen"/>
+        <filter val="Zielwurf Feuerwehrleine"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1004,7 +1004,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>3</v>
       </c>

--- a/info/Bewertung.xlsx
+++ b/info/Bewertung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05_GIT\JuMa_Tir\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A97A90-2113-488D-A88F-C72A7E5C60B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431A56B5-D54B-4D80-B741-AD6423EB487B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="53652" yWindow="-2880" windowWidth="30936" windowHeight="16776" xr2:uid="{AFEFCC93-C23D-44FC-ACFD-BDB8AA63CF66}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="52">
   <si>
     <t>Station</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>(Istzeit - Sollzeit) / Zeitintervall</t>
+  </si>
+  <si>
+    <t>Zeit Felder</t>
   </si>
 </sst>
 </file>
@@ -236,7 +239,10 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -287,28 +293,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E742889C-8821-4005-9075-3A6DDB05D360}" name="Tabelle1" displayName="Tabelle1" ref="A1:M51" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:M51" xr:uid="{E742889C-8821-4005-9075-3A6DDB05D360}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Zielwurf Feuerwehrleine"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{6C5AE5F5-F82C-46DD-807D-0F5BAF0B4415}" name="Station-Nr" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E742889C-8821-4005-9075-3A6DDB05D360}" name="Tabelle1" displayName="Tabelle1" ref="A1:N51" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:N51" xr:uid="{E742889C-8821-4005-9075-3A6DDB05D360}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{6C5AE5F5-F82C-46DD-807D-0F5BAF0B4415}" name="Station-Nr" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{7BA1FAE7-66DA-43CA-8533-7F7E0E739CAB}" name="Station"/>
-    <tableColumn id="7" xr3:uid="{ED744B63-A0F1-42DA-B4C1-E82CDC998749}" name="Position" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{ED744B63-A0F1-42DA-B4C1-E82CDC998749}" name="Position" dataDxfId="9"/>
     <tableColumn id="3" xr3:uid="{9EA51F1D-4DA2-44C5-A3C1-6804D1D95756}" name="Aufgabe"/>
     <tableColumn id="11" xr3:uid="{AC773CA2-253C-4EF5-AE59-048FBB8B5B70}" name="Typ"/>
-    <tableColumn id="12" xr3:uid="{0C155D59-101D-44C6-821B-29230F89411F}" name="Startwert" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{CB97E745-C500-4C83-8E86-1D3020239A89}" name="Teilnehmer" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{2D6D31A4-0308-468C-976B-2F21C9CBD171}" name="Fehler" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{5E8A0EAB-0EB0-42D8-9A7F-BD0883DEFF53}" name="Max-Feldwert" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{1D63DB61-3896-4275-87C6-983B53032476}" name="Sollzeit" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{76551AFA-4492-4D26-B289-A06F28E55B5F}" name="Höchstzeit" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{EB096A5C-56E8-4E2C-A145-EFB1CBF6911F}" name="Zeitintervall" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{D8D27585-9089-48D5-8C75-8379F29326B1}" name="Berechnung Fehler" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{0C155D59-101D-44C6-821B-29230F89411F}" name="Startwert" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{CB97E745-C500-4C83-8E86-1D3020239A89}" name="Teilnehmer" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{2D6D31A4-0308-468C-976B-2F21C9CBD171}" name="Fehler" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{5E8A0EAB-0EB0-42D8-9A7F-BD0883DEFF53}" name="Max-Feldwert" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{1D63DB61-3896-4275-87C6-983B53032476}" name="Sollzeit" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{76551AFA-4492-4D26-B289-A06F28E55B5F}" name="Höchstzeit" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{EB096A5C-56E8-4E2C-A145-EFB1CBF6911F}" name="Zeitintervall" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{D8D27585-9089-48D5-8C75-8379F29326B1}" name="Berechnung Fehler" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{EE8C18F1-0ABB-402B-863E-F119BEDF2A3C}" name="Zeit Felder" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -611,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67D4DE2-7270-41CF-BFB4-28476196B0F3}">
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="1"/>
@@ -625,7 +626,7 @@
     <col min="13" max="13" width="25.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -665,8 +666,11 @@
       <c r="M1" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -697,8 +701,9 @@
       <c r="M2" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -732,8 +737,9 @@
       <c r="M3" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -767,8 +773,9 @@
       <c r="M4" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -802,8 +809,9 @@
       <c r="M5" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -837,8 +845,9 @@
       <c r="M6" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -869,8 +878,9 @@
       <c r="M7" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -904,8 +914,9 @@
       <c r="M8" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -939,8 +950,9 @@
       <c r="M9" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -971,8 +983,9 @@
       <c r="M10" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1003,8 +1016,9 @@
       <c r="M11" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1035,8 +1049,9 @@
       <c r="M12" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -1070,8 +1085,9 @@
       <c r="M13" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -1105,8 +1121,9 @@
       <c r="M14" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -1140,8 +1157,9 @@
       <c r="M15" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -1175,8 +1193,9 @@
       <c r="M16" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -1207,8 +1226,9 @@
       <c r="M17" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -1242,8 +1262,9 @@
       <c r="M18" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -1280,8 +1301,11 @@
       <c r="M19" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -1312,8 +1336,9 @@
       <c r="M20" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -1344,8 +1369,9 @@
       <c r="M21" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -1379,8 +1405,9 @@
       <c r="M22" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -1414,8 +1441,9 @@
       <c r="M23" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N23" s="1"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -1449,8 +1477,9 @@
       <c r="M24" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -1484,8 +1513,9 @@
       <c r="M25" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N25" s="1"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -1516,8 +1546,9 @@
       <c r="M26" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N26" s="1"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -1551,8 +1582,9 @@
       <c r="M27" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N27" s="1"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -1586,8 +1618,9 @@
       <c r="M28" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -1621,8 +1654,9 @@
       <c r="M29" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -1659,8 +1693,11 @@
       <c r="M30" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N30" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -1691,8 +1728,9 @@
       <c r="M31" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -1723,8 +1761,9 @@
       <c r="M32" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N32" s="1"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -1758,8 +1797,9 @@
       <c r="M33" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N33" s="1"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -1793,8 +1833,9 @@
       <c r="M34" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N34" s="1"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -1828,8 +1869,9 @@
       <c r="M35" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N35" s="1"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -1863,8 +1905,9 @@
       <c r="M36" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N36" s="1"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -1895,8 +1938,9 @@
       <c r="M37" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -1927,8 +1971,9 @@
       <c r="M38" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -1959,8 +2004,9 @@
       <c r="M39" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -1991,8 +2037,9 @@
       <c r="M40" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -2026,8 +2073,9 @@
       <c r="M41" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N41" s="1"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>4</v>
       </c>
@@ -2058,8 +2106,9 @@
       <c r="M42" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>4</v>
       </c>
@@ -2093,8 +2142,9 @@
       <c r="M43" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N43" s="1"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>4</v>
       </c>
@@ -2125,8 +2175,9 @@
       <c r="M44" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N44" s="1"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>4</v>
       </c>
@@ -2157,8 +2208,9 @@
       <c r="M45" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N45" s="1"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>4</v>
       </c>
@@ -2189,8 +2241,9 @@
       <c r="M46" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N46" s="1"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>4</v>
       </c>
@@ -2221,8 +2274,9 @@
       <c r="M47" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N47" s="1"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>4</v>
       </c>
@@ -2253,8 +2307,9 @@
       <c r="M48" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N48" s="1"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>4</v>
       </c>
@@ -2285,8 +2340,9 @@
       <c r="M49" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N49" s="1"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>4</v>
       </c>
@@ -2323,8 +2379,11 @@
       <c r="M50" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>4</v>
       </c>
@@ -2355,6 +2414,7 @@
       <c r="M51" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="N51" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/info/Bewertung.xlsx
+++ b/info/Bewertung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05_GIT\JuMa_Tir\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431A56B5-D54B-4D80-B741-AD6423EB487B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C33EF2-832C-4B68-BAAC-EB51F066BFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="53652" yWindow="-2880" windowWidth="30936" windowHeight="16776" xr2:uid="{AFEFCC93-C23D-44FC-ACFD-BDB8AA63CF66}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="82">
   <si>
     <t>Station</t>
   </si>
@@ -195,6 +195,96 @@
   </si>
   <si>
     <t>Zeit Felder</t>
+  </si>
+  <si>
+    <t>Zielspritzen Kübelspritze</t>
+  </si>
+  <si>
+    <t>Ausrollen C-Schlauch</t>
+  </si>
+  <si>
+    <t>C-Schlauch überrollt Begrenzungslinie</t>
+  </si>
+  <si>
+    <t>C-Schlauch erreicht nicht 5 Meter Markierungslinie</t>
+  </si>
+  <si>
+    <t>Kein Überschreiten der Grenzlinie</t>
+  </si>
+  <si>
+    <t>Pumpbeginn nicht vor Kommando „Wasser marsch“</t>
+  </si>
+  <si>
+    <t>C-Schlauch nicht frei geworfen</t>
+  </si>
+  <si>
+    <t>C-Schlauch in den ersten 2 Metern aufgesetzt</t>
+  </si>
+  <si>
+    <t>Knotengestell</t>
+  </si>
+  <si>
+    <t>Knoten oder Stich am Gestell falsch ausgeführt</t>
+  </si>
+  <si>
+    <t>Knoten oder Stich am Gestell nicht ausgeführt</t>
+  </si>
+  <si>
+    <t>Konten oder Stich von anderen Teiln. ausgeführt</t>
+  </si>
+  <si>
+    <t>Anlegen Mastwurf</t>
+  </si>
+  <si>
+    <t>Falsches oder Nichtanlegen des Mastwurfes</t>
+  </si>
+  <si>
+    <t>Fehlen des freien Ende bzw. Ende nicht 3m lang</t>
+  </si>
+  <si>
+    <t>Aufziehen Strahlrohr</t>
+  </si>
+  <si>
+    <t>Nicht Befestigen oder falsches Anlegen der Leine</t>
+  </si>
+  <si>
+    <t>Knoten nicht hinter der 3 m Linie angebracht</t>
+  </si>
+  <si>
+    <t>Beim Aufziehen nicht hinter der 3m Linie gestanden</t>
+  </si>
+  <si>
+    <t>90m Kuppeln</t>
+  </si>
+  <si>
+    <t>Nicht ganz geschlossene Kupplung</t>
+  </si>
+  <si>
+    <t>Brustbund Teilnehmer</t>
+  </si>
+  <si>
+    <t>Falsches Anlegen oder nicht straff am Körper anliegender Brustbund</t>
+  </si>
+  <si>
+    <t>Vergessen des Spierenstichs zur Sicherung</t>
+  </si>
+  <si>
+    <t>Brustbund Selbst</t>
+  </si>
+  <si>
+    <t>Ausrüstungsgegenstände</t>
+  </si>
+  <si>
+    <t>Nicht zugeordnetes Symbol</t>
+  </si>
+  <si>
+    <t>Falsch zugeordnetes Symbol</t>
+  </si>
+  <si>
+    <t>Zielkontrolle</t>
+  </si>
+  <si>
+    <t>Startkarte abgegeben</t>
   </si>
 </sst>
 </file>
@@ -293,8 +383,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E742889C-8821-4005-9075-3A6DDB05D360}" name="Tabelle1" displayName="Tabelle1" ref="A1:N51" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:N51" xr:uid="{E742889C-8821-4005-9075-3A6DDB05D360}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E742889C-8821-4005-9075-3A6DDB05D360}" name="Tabelle1" displayName="Tabelle1" ref="A1:N152" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:N152" xr:uid="{E742889C-8821-4005-9075-3A6DDB05D360}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{6C5AE5F5-F82C-46DD-807D-0F5BAF0B4415}" name="Station-Nr" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{7BA1FAE7-66DA-43CA-8533-7F7E0E739CAB}" name="Station"/>
@@ -612,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67D4DE2-7270-41CF-BFB4-28476196B0F3}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="1"/>
@@ -2416,6 +2506,3573 @@
       </c>
       <c r="N51" s="1"/>
     </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" t="s">
+        <v>39</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G52" s="1">
+        <v>4</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1</v>
+      </c>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N52" s="1"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>5</v>
+      </c>
+      <c r="B53" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="1">
+        <v>2</v>
+      </c>
+      <c r="D53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>4</v>
+      </c>
+      <c r="H53" s="1">
+        <v>10</v>
+      </c>
+      <c r="I53" s="1">
+        <v>4</v>
+      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>5</v>
+      </c>
+      <c r="B54" t="s">
+        <v>52</v>
+      </c>
+      <c r="C54" s="1">
+        <v>3</v>
+      </c>
+      <c r="D54" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>4</v>
+      </c>
+      <c r="H54" s="1">
+        <v>5</v>
+      </c>
+      <c r="I54" s="1">
+        <v>4</v>
+      </c>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C55" s="1">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>4</v>
+      </c>
+      <c r="H55" s="1">
+        <v>5</v>
+      </c>
+      <c r="I55" s="1">
+        <v>4</v>
+      </c>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N55" s="1"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>5</v>
+      </c>
+      <c r="B56" t="s">
+        <v>52</v>
+      </c>
+      <c r="C56" s="1">
+        <v>5</v>
+      </c>
+      <c r="D56" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>4</v>
+      </c>
+      <c r="H56" s="1">
+        <v>10</v>
+      </c>
+      <c r="I56" s="1">
+        <v>4</v>
+      </c>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" s="1">
+        <v>6</v>
+      </c>
+      <c r="D57" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" t="s">
+        <v>39</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G57" s="1">
+        <v>4</v>
+      </c>
+      <c r="H57" s="1">
+        <v>2</v>
+      </c>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N57" s="1"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>5</v>
+      </c>
+      <c r="B58" t="s">
+        <v>52</v>
+      </c>
+      <c r="C58" s="1">
+        <v>7</v>
+      </c>
+      <c r="D58" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58" t="s">
+        <v>42</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>4</v>
+      </c>
+      <c r="H58" s="1">
+        <v>5</v>
+      </c>
+      <c r="I58" s="1">
+        <v>4</v>
+      </c>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N58" s="1"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>5</v>
+      </c>
+      <c r="B59" t="s">
+        <v>52</v>
+      </c>
+      <c r="C59" s="1">
+        <v>8</v>
+      </c>
+      <c r="D59" t="s">
+        <v>57</v>
+      </c>
+      <c r="E59" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>4</v>
+      </c>
+      <c r="H59" s="1">
+        <v>5</v>
+      </c>
+      <c r="I59" s="1">
+        <v>4</v>
+      </c>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N59" s="1"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>52</v>
+      </c>
+      <c r="C60" s="1">
+        <v>9</v>
+      </c>
+      <c r="D60" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" t="s">
+        <v>43</v>
+      </c>
+      <c r="G60" s="1">
+        <v>4</v>
+      </c>
+      <c r="H60" s="1">
+        <v>1</v>
+      </c>
+      <c r="I60" s="1">
+        <v>40</v>
+      </c>
+      <c r="J60" s="1">
+        <v>30</v>
+      </c>
+      <c r="K60" s="1">
+        <v>40</v>
+      </c>
+      <c r="L60" s="1">
+        <v>1</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N60" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>5</v>
+      </c>
+      <c r="B61" t="s">
+        <v>52</v>
+      </c>
+      <c r="C61" s="1">
+        <v>10</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>39</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G61" s="1">
+        <v>4</v>
+      </c>
+      <c r="H61" s="1">
+        <v>1</v>
+      </c>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N61" s="1"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>6</v>
+      </c>
+      <c r="B62" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" t="s">
+        <v>6</v>
+      </c>
+      <c r="E62" t="s">
+        <v>39</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G62" s="1">
+        <v>4</v>
+      </c>
+      <c r="H62" s="1">
+        <v>1</v>
+      </c>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N62" s="1"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>6</v>
+      </c>
+      <c r="B63" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" s="1">
+        <v>2</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" t="s">
+        <v>42</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>4</v>
+      </c>
+      <c r="H63" s="1">
+        <v>10</v>
+      </c>
+      <c r="I63" s="1">
+        <v>4</v>
+      </c>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N63" s="1"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>6</v>
+      </c>
+      <c r="B64" t="s">
+        <v>53</v>
+      </c>
+      <c r="C64" s="1">
+        <v>3</v>
+      </c>
+      <c r="D64" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" t="s">
+        <v>42</v>
+      </c>
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>4</v>
+      </c>
+      <c r="H64" s="1">
+        <v>5</v>
+      </c>
+      <c r="I64" s="1">
+        <v>4</v>
+      </c>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N64" s="1"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>6</v>
+      </c>
+      <c r="B65" t="s">
+        <v>53</v>
+      </c>
+      <c r="C65" s="1">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" t="s">
+        <v>42</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>4</v>
+      </c>
+      <c r="H65" s="1">
+        <v>5</v>
+      </c>
+      <c r="I65" s="1">
+        <v>4</v>
+      </c>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N65" s="1"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>6</v>
+      </c>
+      <c r="B66" t="s">
+        <v>53</v>
+      </c>
+      <c r="C66" s="1">
+        <v>5</v>
+      </c>
+      <c r="D66" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" t="s">
+        <v>42</v>
+      </c>
+      <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>4</v>
+      </c>
+      <c r="H66" s="1">
+        <v>10</v>
+      </c>
+      <c r="I66" s="1">
+        <v>4</v>
+      </c>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N66" s="1"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>6</v>
+      </c>
+      <c r="B67" t="s">
+        <v>53</v>
+      </c>
+      <c r="C67" s="1">
+        <v>6</v>
+      </c>
+      <c r="D67" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" t="s">
+        <v>39</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G67" s="1">
+        <v>4</v>
+      </c>
+      <c r="H67" s="1">
+        <v>2</v>
+      </c>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N67" s="1"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>6</v>
+      </c>
+      <c r="B68" t="s">
+        <v>53</v>
+      </c>
+      <c r="C68" s="1">
+        <v>7</v>
+      </c>
+      <c r="D68" t="s">
+        <v>58</v>
+      </c>
+      <c r="E68" t="s">
+        <v>42</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>4</v>
+      </c>
+      <c r="H68" s="1">
+        <v>5</v>
+      </c>
+      <c r="I68" s="1">
+        <v>4</v>
+      </c>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N68" s="1"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>6</v>
+      </c>
+      <c r="B69" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="1">
+        <v>8</v>
+      </c>
+      <c r="D69" t="s">
+        <v>59</v>
+      </c>
+      <c r="E69" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>4</v>
+      </c>
+      <c r="H69" s="1">
+        <v>5</v>
+      </c>
+      <c r="I69" s="1">
+        <v>4</v>
+      </c>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N69" s="1"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>6</v>
+      </c>
+      <c r="B70" t="s">
+        <v>53</v>
+      </c>
+      <c r="C70" s="1">
+        <v>9</v>
+      </c>
+      <c r="D70" t="s">
+        <v>54</v>
+      </c>
+      <c r="E70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>4</v>
+      </c>
+      <c r="H70" s="1">
+        <v>5</v>
+      </c>
+      <c r="I70" s="1">
+        <v>4</v>
+      </c>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N70" s="1"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>6</v>
+      </c>
+      <c r="B71" t="s">
+        <v>53</v>
+      </c>
+      <c r="C71" s="1">
+        <v>10</v>
+      </c>
+      <c r="D71" t="s">
+        <v>55</v>
+      </c>
+      <c r="E71" t="s">
+        <v>42</v>
+      </c>
+      <c r="F71" s="1">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>4</v>
+      </c>
+      <c r="H71" s="1">
+        <v>5</v>
+      </c>
+      <c r="I71" s="1">
+        <v>4</v>
+      </c>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N71" s="1"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>6</v>
+      </c>
+      <c r="B72" t="s">
+        <v>53</v>
+      </c>
+      <c r="C72" s="1">
+        <v>11</v>
+      </c>
+      <c r="D72" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" t="s">
+        <v>43</v>
+      </c>
+      <c r="G72" s="1">
+        <v>4</v>
+      </c>
+      <c r="H72" s="1">
+        <v>1</v>
+      </c>
+      <c r="I72" s="1">
+        <v>20</v>
+      </c>
+      <c r="J72" s="1">
+        <v>15</v>
+      </c>
+      <c r="K72" s="1">
+        <v>20</v>
+      </c>
+      <c r="L72" s="1">
+        <v>1</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N72" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>6</v>
+      </c>
+      <c r="B73" t="s">
+        <v>53</v>
+      </c>
+      <c r="C73" s="1">
+        <v>12</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" t="s">
+        <v>39</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G73" s="1">
+        <v>4</v>
+      </c>
+      <c r="H73" s="1">
+        <v>1</v>
+      </c>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N73" s="1"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>7</v>
+      </c>
+      <c r="B74" t="s">
+        <v>60</v>
+      </c>
+      <c r="C74" s="1">
+        <v>1</v>
+      </c>
+      <c r="D74" t="s">
+        <v>6</v>
+      </c>
+      <c r="E74" t="s">
+        <v>39</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G74" s="1">
+        <v>4</v>
+      </c>
+      <c r="H74" s="1">
+        <v>1</v>
+      </c>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N74" s="1"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>7</v>
+      </c>
+      <c r="B75" t="s">
+        <v>60</v>
+      </c>
+      <c r="C75" s="1">
+        <v>2</v>
+      </c>
+      <c r="D75" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" t="s">
+        <v>42</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>4</v>
+      </c>
+      <c r="H75" s="1">
+        <v>10</v>
+      </c>
+      <c r="I75" s="1">
+        <v>4</v>
+      </c>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N75" s="1"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>7</v>
+      </c>
+      <c r="B76" t="s">
+        <v>60</v>
+      </c>
+      <c r="C76" s="1">
+        <v>3</v>
+      </c>
+      <c r="D76" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" t="s">
+        <v>42</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>4</v>
+      </c>
+      <c r="H76" s="1">
+        <v>5</v>
+      </c>
+      <c r="I76" s="1">
+        <v>4</v>
+      </c>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N76" s="1"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>7</v>
+      </c>
+      <c r="B77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C77" s="1">
+        <v>4</v>
+      </c>
+      <c r="D77" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" t="s">
+        <v>42</v>
+      </c>
+      <c r="F77" s="1">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>4</v>
+      </c>
+      <c r="H77" s="1">
+        <v>5</v>
+      </c>
+      <c r="I77" s="1">
+        <v>4</v>
+      </c>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N77" s="1"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>7</v>
+      </c>
+      <c r="B78" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="1">
+        <v>5</v>
+      </c>
+      <c r="D78" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" t="s">
+        <v>42</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>4</v>
+      </c>
+      <c r="H78" s="1">
+        <v>10</v>
+      </c>
+      <c r="I78" s="1">
+        <v>4</v>
+      </c>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N78" s="1"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>7</v>
+      </c>
+      <c r="B79" t="s">
+        <v>60</v>
+      </c>
+      <c r="C79" s="1">
+        <v>6</v>
+      </c>
+      <c r="D79" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" t="s">
+        <v>39</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G79" s="1">
+        <v>4</v>
+      </c>
+      <c r="H79" s="1">
+        <v>2</v>
+      </c>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N79" s="1"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>7</v>
+      </c>
+      <c r="B80" t="s">
+        <v>60</v>
+      </c>
+      <c r="C80" s="1">
+        <v>7</v>
+      </c>
+      <c r="D80" t="s">
+        <v>61</v>
+      </c>
+      <c r="E80" t="s">
+        <v>42</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>4</v>
+      </c>
+      <c r="H80" s="1">
+        <v>5</v>
+      </c>
+      <c r="I80" s="1">
+        <v>4</v>
+      </c>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N80" s="1"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>7</v>
+      </c>
+      <c r="B81" t="s">
+        <v>60</v>
+      </c>
+      <c r="C81" s="1">
+        <v>8</v>
+      </c>
+      <c r="D81" t="s">
+        <v>62</v>
+      </c>
+      <c r="E81" t="s">
+        <v>42</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>4</v>
+      </c>
+      <c r="H81" s="1">
+        <v>10</v>
+      </c>
+      <c r="I81" s="1">
+        <v>4</v>
+      </c>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N81" s="1"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>7</v>
+      </c>
+      <c r="B82" t="s">
+        <v>60</v>
+      </c>
+      <c r="C82" s="1">
+        <v>9</v>
+      </c>
+      <c r="D82" t="s">
+        <v>63</v>
+      </c>
+      <c r="E82" t="s">
+        <v>42</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>4</v>
+      </c>
+      <c r="H82" s="1">
+        <v>5</v>
+      </c>
+      <c r="I82" s="1">
+        <v>4</v>
+      </c>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N82" s="1"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>7</v>
+      </c>
+      <c r="B83" t="s">
+        <v>60</v>
+      </c>
+      <c r="C83" s="1">
+        <v>10</v>
+      </c>
+      <c r="D83" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" t="s">
+        <v>43</v>
+      </c>
+      <c r="G83" s="1">
+        <v>4</v>
+      </c>
+      <c r="H83" s="1">
+        <v>1</v>
+      </c>
+      <c r="I83" s="1">
+        <v>30</v>
+      </c>
+      <c r="J83" s="1">
+        <v>20</v>
+      </c>
+      <c r="K83" s="1">
+        <v>30</v>
+      </c>
+      <c r="L83" s="1">
+        <v>1</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N83" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>7</v>
+      </c>
+      <c r="B84" t="s">
+        <v>60</v>
+      </c>
+      <c r="C84" s="1">
+        <v>11</v>
+      </c>
+      <c r="D84" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" t="s">
+        <v>39</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G84" s="1">
+        <v>4</v>
+      </c>
+      <c r="H84" s="1">
+        <v>1</v>
+      </c>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N84" s="1"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>8</v>
+      </c>
+      <c r="B85" t="s">
+        <v>64</v>
+      </c>
+      <c r="C85" s="1">
+        <v>1</v>
+      </c>
+      <c r="D85" t="s">
+        <v>6</v>
+      </c>
+      <c r="E85" t="s">
+        <v>39</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G85" s="1">
+        <v>4</v>
+      </c>
+      <c r="H85" s="1">
+        <v>1</v>
+      </c>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N85" s="1"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>8</v>
+      </c>
+      <c r="B86" t="s">
+        <v>64</v>
+      </c>
+      <c r="C86" s="1">
+        <v>2</v>
+      </c>
+      <c r="D86" t="s">
+        <v>7</v>
+      </c>
+      <c r="E86" t="s">
+        <v>42</v>
+      </c>
+      <c r="F86" s="1">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1">
+        <v>4</v>
+      </c>
+      <c r="H86" s="1">
+        <v>10</v>
+      </c>
+      <c r="I86" s="1">
+        <v>4</v>
+      </c>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N86" s="1"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>8</v>
+      </c>
+      <c r="B87" t="s">
+        <v>64</v>
+      </c>
+      <c r="C87" s="1">
+        <v>3</v>
+      </c>
+      <c r="D87" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" t="s">
+        <v>42</v>
+      </c>
+      <c r="F87" s="1">
+        <v>0</v>
+      </c>
+      <c r="G87" s="1">
+        <v>4</v>
+      </c>
+      <c r="H87" s="1">
+        <v>5</v>
+      </c>
+      <c r="I87" s="1">
+        <v>4</v>
+      </c>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N87" s="1"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>8</v>
+      </c>
+      <c r="B88" t="s">
+        <v>64</v>
+      </c>
+      <c r="C88" s="1">
+        <v>4</v>
+      </c>
+      <c r="D88" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" t="s">
+        <v>42</v>
+      </c>
+      <c r="F88" s="1">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>4</v>
+      </c>
+      <c r="H88" s="1">
+        <v>5</v>
+      </c>
+      <c r="I88" s="1">
+        <v>4</v>
+      </c>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N88" s="1"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>8</v>
+      </c>
+      <c r="B89" t="s">
+        <v>64</v>
+      </c>
+      <c r="C89" s="1">
+        <v>5</v>
+      </c>
+      <c r="D89" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" t="s">
+        <v>42</v>
+      </c>
+      <c r="F89" s="1">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>4</v>
+      </c>
+      <c r="H89" s="1">
+        <v>10</v>
+      </c>
+      <c r="I89" s="1">
+        <v>4</v>
+      </c>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N89" s="1"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>8</v>
+      </c>
+      <c r="B90" t="s">
+        <v>64</v>
+      </c>
+      <c r="C90" s="1">
+        <v>6</v>
+      </c>
+      <c r="D90" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" t="s">
+        <v>39</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G90" s="1">
+        <v>4</v>
+      </c>
+      <c r="H90" s="1">
+        <v>2</v>
+      </c>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N90" s="1"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>8</v>
+      </c>
+      <c r="B91" t="s">
+        <v>64</v>
+      </c>
+      <c r="C91" s="1">
+        <v>7</v>
+      </c>
+      <c r="D91" t="s">
+        <v>65</v>
+      </c>
+      <c r="E91" t="s">
+        <v>42</v>
+      </c>
+      <c r="F91" s="1">
+        <v>0</v>
+      </c>
+      <c r="G91" s="1">
+        <v>4</v>
+      </c>
+      <c r="H91" s="1">
+        <v>5</v>
+      </c>
+      <c r="I91" s="1">
+        <v>4</v>
+      </c>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N91" s="1"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>8</v>
+      </c>
+      <c r="B92" t="s">
+        <v>64</v>
+      </c>
+      <c r="C92" s="1">
+        <v>8</v>
+      </c>
+      <c r="D92" t="s">
+        <v>66</v>
+      </c>
+      <c r="E92" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" s="1">
+        <v>0</v>
+      </c>
+      <c r="G92" s="1">
+        <v>4</v>
+      </c>
+      <c r="H92" s="1">
+        <v>2</v>
+      </c>
+      <c r="I92" s="1">
+        <v>4</v>
+      </c>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N92" s="1"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>8</v>
+      </c>
+      <c r="B93" t="s">
+        <v>64</v>
+      </c>
+      <c r="C93" s="1">
+        <v>9</v>
+      </c>
+      <c r="D93" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93" t="s">
+        <v>43</v>
+      </c>
+      <c r="G93" s="1">
+        <v>4</v>
+      </c>
+      <c r="H93" s="1">
+        <v>1</v>
+      </c>
+      <c r="I93" s="1">
+        <v>15</v>
+      </c>
+      <c r="J93" s="1">
+        <v>10</v>
+      </c>
+      <c r="K93" s="1">
+        <v>15</v>
+      </c>
+      <c r="L93" s="1">
+        <v>1</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N93" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>8</v>
+      </c>
+      <c r="B94" t="s">
+        <v>64</v>
+      </c>
+      <c r="C94" s="1">
+        <v>10</v>
+      </c>
+      <c r="D94" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" t="s">
+        <v>39</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G94" s="1">
+        <v>4</v>
+      </c>
+      <c r="H94" s="1">
+        <v>1</v>
+      </c>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N94" s="1"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>9</v>
+      </c>
+      <c r="B95" t="s">
+        <v>67</v>
+      </c>
+      <c r="C95" s="1">
+        <v>1</v>
+      </c>
+      <c r="D95" t="s">
+        <v>6</v>
+      </c>
+      <c r="E95" t="s">
+        <v>39</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G95" s="1">
+        <v>4</v>
+      </c>
+      <c r="H95" s="1">
+        <v>1</v>
+      </c>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1"/>
+      <c r="M95" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N95" s="1"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>9</v>
+      </c>
+      <c r="B96" t="s">
+        <v>67</v>
+      </c>
+      <c r="C96" s="1">
+        <v>2</v>
+      </c>
+      <c r="D96" t="s">
+        <v>7</v>
+      </c>
+      <c r="E96" t="s">
+        <v>42</v>
+      </c>
+      <c r="F96" s="1">
+        <v>0</v>
+      </c>
+      <c r="G96" s="1">
+        <v>4</v>
+      </c>
+      <c r="H96" s="1">
+        <v>10</v>
+      </c>
+      <c r="I96" s="1">
+        <v>4</v>
+      </c>
+      <c r="J96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N96" s="1"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>9</v>
+      </c>
+      <c r="B97" t="s">
+        <v>67</v>
+      </c>
+      <c r="C97" s="1">
+        <v>3</v>
+      </c>
+      <c r="D97" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" t="s">
+        <v>42</v>
+      </c>
+      <c r="F97" s="1">
+        <v>0</v>
+      </c>
+      <c r="G97" s="1">
+        <v>4</v>
+      </c>
+      <c r="H97" s="1">
+        <v>5</v>
+      </c>
+      <c r="I97" s="1">
+        <v>4</v>
+      </c>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
+      <c r="M97" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N97" s="1"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>9</v>
+      </c>
+      <c r="B98" t="s">
+        <v>67</v>
+      </c>
+      <c r="C98" s="1">
+        <v>4</v>
+      </c>
+      <c r="D98" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" t="s">
+        <v>42</v>
+      </c>
+      <c r="F98" s="1">
+        <v>0</v>
+      </c>
+      <c r="G98" s="1">
+        <v>4</v>
+      </c>
+      <c r="H98" s="1">
+        <v>5</v>
+      </c>
+      <c r="I98" s="1">
+        <v>4</v>
+      </c>
+      <c r="J98" s="1"/>
+      <c r="K98" s="1"/>
+      <c r="L98" s="1"/>
+      <c r="M98" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N98" s="1"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>9</v>
+      </c>
+      <c r="B99" t="s">
+        <v>67</v>
+      </c>
+      <c r="C99" s="1">
+        <v>5</v>
+      </c>
+      <c r="D99" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99" t="s">
+        <v>42</v>
+      </c>
+      <c r="F99" s="1">
+        <v>0</v>
+      </c>
+      <c r="G99" s="1">
+        <v>4</v>
+      </c>
+      <c r="H99" s="1">
+        <v>10</v>
+      </c>
+      <c r="I99" s="1">
+        <v>4</v>
+      </c>
+      <c r="J99" s="1"/>
+      <c r="K99" s="1"/>
+      <c r="L99" s="1"/>
+      <c r="M99" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N99" s="1"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>9</v>
+      </c>
+      <c r="B100" t="s">
+        <v>67</v>
+      </c>
+      <c r="C100" s="1">
+        <v>6</v>
+      </c>
+      <c r="D100" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" t="s">
+        <v>39</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G100" s="1">
+        <v>4</v>
+      </c>
+      <c r="H100" s="1">
+        <v>2</v>
+      </c>
+      <c r="J100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N100" s="1"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>9</v>
+      </c>
+      <c r="B101" t="s">
+        <v>67</v>
+      </c>
+      <c r="C101" s="1">
+        <v>7</v>
+      </c>
+      <c r="D101" t="s">
+        <v>68</v>
+      </c>
+      <c r="E101" t="s">
+        <v>42</v>
+      </c>
+      <c r="F101" s="1">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1">
+        <v>4</v>
+      </c>
+      <c r="H101" s="1">
+        <v>5</v>
+      </c>
+      <c r="I101" s="1">
+        <v>4</v>
+      </c>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N101" s="1"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>9</v>
+      </c>
+      <c r="B102" t="s">
+        <v>67</v>
+      </c>
+      <c r="C102" s="1">
+        <v>8</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" t="s">
+        <v>42</v>
+      </c>
+      <c r="F102" s="1">
+        <v>0</v>
+      </c>
+      <c r="G102" s="1">
+        <v>4</v>
+      </c>
+      <c r="H102" s="1">
+        <v>5</v>
+      </c>
+      <c r="I102" s="1">
+        <v>4</v>
+      </c>
+      <c r="J102" s="1"/>
+      <c r="K102" s="1"/>
+      <c r="L102" s="1"/>
+      <c r="M102" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N102" s="1"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>9</v>
+      </c>
+      <c r="B103" t="s">
+        <v>67</v>
+      </c>
+      <c r="C103" s="1">
+        <v>9</v>
+      </c>
+      <c r="D103" t="s">
+        <v>70</v>
+      </c>
+      <c r="E103" t="s">
+        <v>42</v>
+      </c>
+      <c r="F103" s="1">
+        <v>0</v>
+      </c>
+      <c r="G103" s="1">
+        <v>4</v>
+      </c>
+      <c r="H103" s="1">
+        <v>5</v>
+      </c>
+      <c r="I103" s="1">
+        <v>4</v>
+      </c>
+      <c r="J103" s="1"/>
+      <c r="K103" s="1"/>
+      <c r="L103" s="1"/>
+      <c r="M103" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N103" s="1"/>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>9</v>
+      </c>
+      <c r="B104" t="s">
+        <v>67</v>
+      </c>
+      <c r="C104" s="1">
+        <v>10</v>
+      </c>
+      <c r="D104" t="s">
+        <v>17</v>
+      </c>
+      <c r="E104" t="s">
+        <v>43</v>
+      </c>
+      <c r="H104" s="1">
+        <v>1</v>
+      </c>
+      <c r="I104" s="1">
+        <v>35</v>
+      </c>
+      <c r="J104" s="1">
+        <v>25</v>
+      </c>
+      <c r="K104" s="1">
+        <v>35</v>
+      </c>
+      <c r="L104" s="1">
+        <v>1</v>
+      </c>
+      <c r="M104" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N104" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>9</v>
+      </c>
+      <c r="B105" t="s">
+        <v>67</v>
+      </c>
+      <c r="C105" s="1">
+        <v>11</v>
+      </c>
+      <c r="D105" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" t="s">
+        <v>39</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G105" s="1">
+        <v>4</v>
+      </c>
+      <c r="H105" s="1">
+        <v>1</v>
+      </c>
+      <c r="J105" s="1"/>
+      <c r="K105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N105" s="1"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>10</v>
+      </c>
+      <c r="B106" t="s">
+        <v>71</v>
+      </c>
+      <c r="C106" s="1">
+        <v>1</v>
+      </c>
+      <c r="D106" t="s">
+        <v>6</v>
+      </c>
+      <c r="E106" t="s">
+        <v>39</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G106" s="1">
+        <v>4</v>
+      </c>
+      <c r="H106" s="1">
+        <v>1</v>
+      </c>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N106" s="1"/>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>10</v>
+      </c>
+      <c r="B107" t="s">
+        <v>71</v>
+      </c>
+      <c r="C107" s="1">
+        <v>2</v>
+      </c>
+      <c r="D107" t="s">
+        <v>7</v>
+      </c>
+      <c r="E107" t="s">
+        <v>42</v>
+      </c>
+      <c r="F107" s="1">
+        <v>0</v>
+      </c>
+      <c r="G107" s="1">
+        <v>4</v>
+      </c>
+      <c r="H107" s="1">
+        <v>10</v>
+      </c>
+      <c r="I107" s="1">
+        <v>4</v>
+      </c>
+      <c r="J107" s="1"/>
+      <c r="K107" s="1"/>
+      <c r="L107" s="1"/>
+      <c r="M107" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N107" s="1"/>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>10</v>
+      </c>
+      <c r="B108" t="s">
+        <v>71</v>
+      </c>
+      <c r="C108" s="1">
+        <v>3</v>
+      </c>
+      <c r="D108" t="s">
+        <v>8</v>
+      </c>
+      <c r="E108" t="s">
+        <v>42</v>
+      </c>
+      <c r="F108" s="1">
+        <v>0</v>
+      </c>
+      <c r="G108" s="1">
+        <v>4</v>
+      </c>
+      <c r="H108" s="1">
+        <v>5</v>
+      </c>
+      <c r="I108" s="1">
+        <v>4</v>
+      </c>
+      <c r="J108" s="1"/>
+      <c r="K108" s="1"/>
+      <c r="L108" s="1"/>
+      <c r="M108" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N108" s="1"/>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>10</v>
+      </c>
+      <c r="B109" t="s">
+        <v>71</v>
+      </c>
+      <c r="C109" s="1">
+        <v>4</v>
+      </c>
+      <c r="D109" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" t="s">
+        <v>42</v>
+      </c>
+      <c r="F109" s="1">
+        <v>0</v>
+      </c>
+      <c r="G109" s="1">
+        <v>4</v>
+      </c>
+      <c r="H109" s="1">
+        <v>5</v>
+      </c>
+      <c r="I109" s="1">
+        <v>4</v>
+      </c>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N109" s="1"/>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>10</v>
+      </c>
+      <c r="B110" t="s">
+        <v>71</v>
+      </c>
+      <c r="C110" s="1">
+        <v>5</v>
+      </c>
+      <c r="D110" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" t="s">
+        <v>42</v>
+      </c>
+      <c r="F110" s="1">
+        <v>0</v>
+      </c>
+      <c r="G110" s="1">
+        <v>4</v>
+      </c>
+      <c r="H110" s="1">
+        <v>10</v>
+      </c>
+      <c r="I110" s="1">
+        <v>4</v>
+      </c>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N110" s="1"/>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>10</v>
+      </c>
+      <c r="B111" t="s">
+        <v>71</v>
+      </c>
+      <c r="C111" s="1">
+        <v>6</v>
+      </c>
+      <c r="D111" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" t="s">
+        <v>39</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G111" s="1">
+        <v>4</v>
+      </c>
+      <c r="H111" s="1">
+        <v>2</v>
+      </c>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
+      <c r="M111" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N111" s="1"/>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>10</v>
+      </c>
+      <c r="B112" t="s">
+        <v>71</v>
+      </c>
+      <c r="C112" s="1">
+        <v>7</v>
+      </c>
+      <c r="D112" t="s">
+        <v>72</v>
+      </c>
+      <c r="E112" t="s">
+        <v>42</v>
+      </c>
+      <c r="F112" s="1">
+        <v>0</v>
+      </c>
+      <c r="G112" s="1">
+        <v>4</v>
+      </c>
+      <c r="H112" s="1">
+        <v>3</v>
+      </c>
+      <c r="I112" s="1">
+        <v>12</v>
+      </c>
+      <c r="J112" s="1"/>
+      <c r="K112" s="1"/>
+      <c r="L112" s="1"/>
+      <c r="M112" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N112" s="1"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>10</v>
+      </c>
+      <c r="B113" t="s">
+        <v>71</v>
+      </c>
+      <c r="C113" s="1">
+        <v>8</v>
+      </c>
+      <c r="D113" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" t="s">
+        <v>43</v>
+      </c>
+      <c r="H113" s="1">
+        <v>1</v>
+      </c>
+      <c r="I113" s="1">
+        <v>90</v>
+      </c>
+      <c r="J113" s="1">
+        <v>55</v>
+      </c>
+      <c r="K113" s="1">
+        <v>90</v>
+      </c>
+      <c r="L113" s="1">
+        <v>1</v>
+      </c>
+      <c r="M113" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N113" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>10</v>
+      </c>
+      <c r="B114" t="s">
+        <v>71</v>
+      </c>
+      <c r="C114" s="1">
+        <v>9</v>
+      </c>
+      <c r="D114" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" t="s">
+        <v>39</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G114" s="1">
+        <v>4</v>
+      </c>
+      <c r="H114" s="1">
+        <v>1</v>
+      </c>
+      <c r="J114" s="1"/>
+      <c r="K114" s="1"/>
+      <c r="L114" s="1"/>
+      <c r="M114" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N114" s="1"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>11</v>
+      </c>
+      <c r="B115" t="s">
+        <v>73</v>
+      </c>
+      <c r="C115" s="1">
+        <v>1</v>
+      </c>
+      <c r="D115" t="s">
+        <v>6</v>
+      </c>
+      <c r="E115" t="s">
+        <v>39</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G115" s="1">
+        <v>4</v>
+      </c>
+      <c r="H115" s="1">
+        <v>1</v>
+      </c>
+      <c r="J115" s="1"/>
+      <c r="K115" s="1"/>
+      <c r="L115" s="1"/>
+      <c r="M115" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N115" s="1"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>11</v>
+      </c>
+      <c r="B116" t="s">
+        <v>73</v>
+      </c>
+      <c r="C116" s="1">
+        <v>2</v>
+      </c>
+      <c r="D116" t="s">
+        <v>7</v>
+      </c>
+      <c r="E116" t="s">
+        <v>42</v>
+      </c>
+      <c r="F116" s="1">
+        <v>0</v>
+      </c>
+      <c r="G116" s="1">
+        <v>4</v>
+      </c>
+      <c r="H116" s="1">
+        <v>10</v>
+      </c>
+      <c r="I116" s="1">
+        <v>4</v>
+      </c>
+      <c r="J116" s="1"/>
+      <c r="K116" s="1"/>
+      <c r="L116" s="1"/>
+      <c r="M116" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N116" s="1"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>11</v>
+      </c>
+      <c r="B117" t="s">
+        <v>73</v>
+      </c>
+      <c r="C117" s="1">
+        <v>3</v>
+      </c>
+      <c r="D117" t="s">
+        <v>8</v>
+      </c>
+      <c r="E117" t="s">
+        <v>42</v>
+      </c>
+      <c r="F117" s="1">
+        <v>0</v>
+      </c>
+      <c r="G117" s="1">
+        <v>4</v>
+      </c>
+      <c r="H117" s="1">
+        <v>5</v>
+      </c>
+      <c r="I117" s="1">
+        <v>4</v>
+      </c>
+      <c r="J117" s="1"/>
+      <c r="K117" s="1"/>
+      <c r="L117" s="1"/>
+      <c r="M117" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N117" s="1"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>11</v>
+      </c>
+      <c r="B118" t="s">
+        <v>73</v>
+      </c>
+      <c r="C118" s="1">
+        <v>4</v>
+      </c>
+      <c r="D118" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" t="s">
+        <v>42</v>
+      </c>
+      <c r="F118" s="1">
+        <v>0</v>
+      </c>
+      <c r="G118" s="1">
+        <v>4</v>
+      </c>
+      <c r="H118" s="1">
+        <v>5</v>
+      </c>
+      <c r="I118" s="1">
+        <v>4</v>
+      </c>
+      <c r="J118" s="1"/>
+      <c r="K118" s="1"/>
+      <c r="L118" s="1"/>
+      <c r="M118" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N118" s="1"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>11</v>
+      </c>
+      <c r="B119" t="s">
+        <v>73</v>
+      </c>
+      <c r="C119" s="1">
+        <v>5</v>
+      </c>
+      <c r="D119" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119" t="s">
+        <v>42</v>
+      </c>
+      <c r="F119" s="1">
+        <v>0</v>
+      </c>
+      <c r="G119" s="1">
+        <v>4</v>
+      </c>
+      <c r="H119" s="1">
+        <v>10</v>
+      </c>
+      <c r="I119" s="1">
+        <v>4</v>
+      </c>
+      <c r="J119" s="1"/>
+      <c r="K119" s="1"/>
+      <c r="L119" s="1"/>
+      <c r="M119" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N119" s="1"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>11</v>
+      </c>
+      <c r="B120" t="s">
+        <v>73</v>
+      </c>
+      <c r="C120" s="1">
+        <v>6</v>
+      </c>
+      <c r="D120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" t="s">
+        <v>39</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G120" s="1">
+        <v>4</v>
+      </c>
+      <c r="H120" s="1">
+        <v>2</v>
+      </c>
+      <c r="J120" s="1"/>
+      <c r="K120" s="1"/>
+      <c r="L120" s="1"/>
+      <c r="M120" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N120" s="1"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>11</v>
+      </c>
+      <c r="B121" t="s">
+        <v>73</v>
+      </c>
+      <c r="C121" s="1">
+        <v>7</v>
+      </c>
+      <c r="D121" t="s">
+        <v>74</v>
+      </c>
+      <c r="E121" t="s">
+        <v>42</v>
+      </c>
+      <c r="F121" s="1">
+        <v>0</v>
+      </c>
+      <c r="G121" s="1">
+        <v>4</v>
+      </c>
+      <c r="H121" s="1">
+        <v>5</v>
+      </c>
+      <c r="I121" s="1">
+        <v>4</v>
+      </c>
+      <c r="J121" s="1"/>
+      <c r="K121" s="1"/>
+      <c r="L121" s="1"/>
+      <c r="M121" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N121" s="1"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>11</v>
+      </c>
+      <c r="B122" t="s">
+        <v>73</v>
+      </c>
+      <c r="C122" s="1">
+        <v>8</v>
+      </c>
+      <c r="D122" t="s">
+        <v>75</v>
+      </c>
+      <c r="E122" t="s">
+        <v>42</v>
+      </c>
+      <c r="F122" s="1">
+        <v>0</v>
+      </c>
+      <c r="G122" s="1">
+        <v>4</v>
+      </c>
+      <c r="H122" s="1">
+        <v>3</v>
+      </c>
+      <c r="I122" s="1">
+        <v>4</v>
+      </c>
+      <c r="J122" s="1"/>
+      <c r="K122" s="1"/>
+      <c r="L122" s="1"/>
+      <c r="M122" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N122" s="1"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>11</v>
+      </c>
+      <c r="B123" t="s">
+        <v>73</v>
+      </c>
+      <c r="C123" s="1">
+        <v>9</v>
+      </c>
+      <c r="D123" t="s">
+        <v>17</v>
+      </c>
+      <c r="E123" t="s">
+        <v>43</v>
+      </c>
+      <c r="I123" s="1">
+        <v>50</v>
+      </c>
+      <c r="J123" s="1">
+        <v>40</v>
+      </c>
+      <c r="K123" s="1">
+        <v>50</v>
+      </c>
+      <c r="L123" s="1">
+        <v>1</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N123" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>11</v>
+      </c>
+      <c r="B124" t="s">
+        <v>73</v>
+      </c>
+      <c r="C124" s="1">
+        <v>10</v>
+      </c>
+      <c r="D124" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" t="s">
+        <v>39</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G124" s="1">
+        <v>4</v>
+      </c>
+      <c r="H124" s="1">
+        <v>1</v>
+      </c>
+      <c r="J124" s="1"/>
+      <c r="K124" s="1"/>
+      <c r="L124" s="1"/>
+      <c r="M124" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N124" s="1"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>12</v>
+      </c>
+      <c r="B125" t="s">
+        <v>76</v>
+      </c>
+      <c r="C125" s="1">
+        <v>1</v>
+      </c>
+      <c r="D125" t="s">
+        <v>6</v>
+      </c>
+      <c r="E125" t="s">
+        <v>39</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G125" s="1">
+        <v>4</v>
+      </c>
+      <c r="H125" s="1">
+        <v>1</v>
+      </c>
+      <c r="J125" s="1"/>
+      <c r="K125" s="1"/>
+      <c r="L125" s="1"/>
+      <c r="M125" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N125" s="1"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>12</v>
+      </c>
+      <c r="B126" t="s">
+        <v>76</v>
+      </c>
+      <c r="C126" s="1">
+        <v>2</v>
+      </c>
+      <c r="D126" t="s">
+        <v>7</v>
+      </c>
+      <c r="E126" t="s">
+        <v>42</v>
+      </c>
+      <c r="F126" s="1">
+        <v>0</v>
+      </c>
+      <c r="G126" s="1">
+        <v>4</v>
+      </c>
+      <c r="H126" s="1">
+        <v>10</v>
+      </c>
+      <c r="I126" s="1">
+        <v>4</v>
+      </c>
+      <c r="J126" s="1"/>
+      <c r="K126" s="1"/>
+      <c r="L126" s="1"/>
+      <c r="M126" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N126" s="1"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>12</v>
+      </c>
+      <c r="B127" t="s">
+        <v>76</v>
+      </c>
+      <c r="C127" s="1">
+        <v>3</v>
+      </c>
+      <c r="D127" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" t="s">
+        <v>42</v>
+      </c>
+      <c r="F127" s="1">
+        <v>0</v>
+      </c>
+      <c r="G127" s="1">
+        <v>4</v>
+      </c>
+      <c r="H127" s="1">
+        <v>5</v>
+      </c>
+      <c r="I127" s="1">
+        <v>4</v>
+      </c>
+      <c r="J127" s="1"/>
+      <c r="K127" s="1"/>
+      <c r="L127" s="1"/>
+      <c r="M127" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N127" s="1"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>12</v>
+      </c>
+      <c r="B128" t="s">
+        <v>76</v>
+      </c>
+      <c r="C128" s="1">
+        <v>4</v>
+      </c>
+      <c r="D128" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" t="s">
+        <v>42</v>
+      </c>
+      <c r="F128" s="1">
+        <v>0</v>
+      </c>
+      <c r="G128" s="1">
+        <v>4</v>
+      </c>
+      <c r="H128" s="1">
+        <v>5</v>
+      </c>
+      <c r="I128" s="1">
+        <v>4</v>
+      </c>
+      <c r="J128" s="1"/>
+      <c r="K128" s="1"/>
+      <c r="L128" s="1"/>
+      <c r="M128" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N128" s="1"/>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>12</v>
+      </c>
+      <c r="B129" t="s">
+        <v>76</v>
+      </c>
+      <c r="C129" s="1">
+        <v>5</v>
+      </c>
+      <c r="D129" t="s">
+        <v>10</v>
+      </c>
+      <c r="E129" t="s">
+        <v>42</v>
+      </c>
+      <c r="F129" s="1">
+        <v>0</v>
+      </c>
+      <c r="G129" s="1">
+        <v>4</v>
+      </c>
+      <c r="H129" s="1">
+        <v>10</v>
+      </c>
+      <c r="I129" s="1">
+        <v>4</v>
+      </c>
+      <c r="J129" s="1"/>
+      <c r="K129" s="1"/>
+      <c r="L129" s="1"/>
+      <c r="M129" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N129" s="1"/>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>12</v>
+      </c>
+      <c r="B130" t="s">
+        <v>76</v>
+      </c>
+      <c r="C130" s="1">
+        <v>6</v>
+      </c>
+      <c r="D130" t="s">
+        <v>35</v>
+      </c>
+      <c r="E130" t="s">
+        <v>39</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G130" s="1">
+        <v>4</v>
+      </c>
+      <c r="H130" s="1">
+        <v>2</v>
+      </c>
+      <c r="J130" s="1"/>
+      <c r="K130" s="1"/>
+      <c r="L130" s="1"/>
+      <c r="M130" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N130" s="1"/>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>12</v>
+      </c>
+      <c r="B131" t="s">
+        <v>76</v>
+      </c>
+      <c r="C131" s="1">
+        <v>7</v>
+      </c>
+      <c r="D131" t="s">
+        <v>74</v>
+      </c>
+      <c r="E131" t="s">
+        <v>42</v>
+      </c>
+      <c r="F131" s="1">
+        <v>0</v>
+      </c>
+      <c r="G131" s="1">
+        <v>4</v>
+      </c>
+      <c r="H131" s="1">
+        <v>5</v>
+      </c>
+      <c r="I131" s="1">
+        <v>4</v>
+      </c>
+      <c r="J131" s="1"/>
+      <c r="K131" s="1"/>
+      <c r="L131" s="1"/>
+      <c r="M131" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N131" s="1"/>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>12</v>
+      </c>
+      <c r="B132" t="s">
+        <v>76</v>
+      </c>
+      <c r="C132" s="1">
+        <v>8</v>
+      </c>
+      <c r="D132" t="s">
+        <v>75</v>
+      </c>
+      <c r="E132" t="s">
+        <v>42</v>
+      </c>
+      <c r="F132" s="1">
+        <v>0</v>
+      </c>
+      <c r="G132" s="1">
+        <v>4</v>
+      </c>
+      <c r="H132" s="1">
+        <v>3</v>
+      </c>
+      <c r="I132" s="1">
+        <v>4</v>
+      </c>
+      <c r="J132" s="1"/>
+      <c r="K132" s="1"/>
+      <c r="L132" s="1"/>
+      <c r="M132" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N132" s="1"/>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>12</v>
+      </c>
+      <c r="B133" t="s">
+        <v>76</v>
+      </c>
+      <c r="C133" s="1">
+        <v>9</v>
+      </c>
+      <c r="D133" t="s">
+        <v>17</v>
+      </c>
+      <c r="E133" t="s">
+        <v>43</v>
+      </c>
+      <c r="I133" s="1">
+        <v>50</v>
+      </c>
+      <c r="J133" s="1">
+        <v>40</v>
+      </c>
+      <c r="K133" s="1">
+        <v>50</v>
+      </c>
+      <c r="L133" s="1">
+        <v>1</v>
+      </c>
+      <c r="M133" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N133" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>12</v>
+      </c>
+      <c r="B134" t="s">
+        <v>76</v>
+      </c>
+      <c r="C134" s="1">
+        <v>10</v>
+      </c>
+      <c r="D134" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" t="s">
+        <v>39</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G134" s="1">
+        <v>4</v>
+      </c>
+      <c r="H134" s="1">
+        <v>1</v>
+      </c>
+      <c r="J134" s="1"/>
+      <c r="K134" s="1"/>
+      <c r="L134" s="1"/>
+      <c r="M134" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N134" s="1"/>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>13</v>
+      </c>
+      <c r="B135" t="s">
+        <v>77</v>
+      </c>
+      <c r="C135" s="1">
+        <v>1</v>
+      </c>
+      <c r="D135" t="s">
+        <v>6</v>
+      </c>
+      <c r="E135" t="s">
+        <v>39</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G135" s="1">
+        <v>4</v>
+      </c>
+      <c r="H135" s="1">
+        <v>1</v>
+      </c>
+      <c r="J135" s="1"/>
+      <c r="K135" s="1"/>
+      <c r="L135" s="1"/>
+      <c r="M135" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N135" s="1"/>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>13</v>
+      </c>
+      <c r="B136" t="s">
+        <v>77</v>
+      </c>
+      <c r="C136" s="1">
+        <v>2</v>
+      </c>
+      <c r="D136" t="s">
+        <v>7</v>
+      </c>
+      <c r="E136" t="s">
+        <v>42</v>
+      </c>
+      <c r="F136" s="1">
+        <v>0</v>
+      </c>
+      <c r="G136" s="1">
+        <v>4</v>
+      </c>
+      <c r="H136" s="1">
+        <v>10</v>
+      </c>
+      <c r="I136" s="1">
+        <v>4</v>
+      </c>
+      <c r="J136" s="1"/>
+      <c r="K136" s="1"/>
+      <c r="L136" s="1"/>
+      <c r="M136" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N136" s="1"/>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>13</v>
+      </c>
+      <c r="B137" t="s">
+        <v>77</v>
+      </c>
+      <c r="C137" s="1">
+        <v>3</v>
+      </c>
+      <c r="D137" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" t="s">
+        <v>42</v>
+      </c>
+      <c r="F137" s="1">
+        <v>0</v>
+      </c>
+      <c r="G137" s="1">
+        <v>4</v>
+      </c>
+      <c r="H137" s="1">
+        <v>5</v>
+      </c>
+      <c r="I137" s="1">
+        <v>4</v>
+      </c>
+      <c r="J137" s="1"/>
+      <c r="K137" s="1"/>
+      <c r="L137" s="1"/>
+      <c r="M137" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N137" s="1"/>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>13</v>
+      </c>
+      <c r="B138" t="s">
+        <v>77</v>
+      </c>
+      <c r="C138" s="1">
+        <v>4</v>
+      </c>
+      <c r="D138" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138" t="s">
+        <v>42</v>
+      </c>
+      <c r="F138" s="1">
+        <v>0</v>
+      </c>
+      <c r="G138" s="1">
+        <v>4</v>
+      </c>
+      <c r="H138" s="1">
+        <v>5</v>
+      </c>
+      <c r="I138" s="1">
+        <v>4</v>
+      </c>
+      <c r="J138" s="1"/>
+      <c r="K138" s="1"/>
+      <c r="L138" s="1"/>
+      <c r="M138" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N138" s="1"/>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>13</v>
+      </c>
+      <c r="B139" t="s">
+        <v>77</v>
+      </c>
+      <c r="C139" s="1">
+        <v>5</v>
+      </c>
+      <c r="D139" t="s">
+        <v>10</v>
+      </c>
+      <c r="E139" t="s">
+        <v>42</v>
+      </c>
+      <c r="F139" s="1">
+        <v>0</v>
+      </c>
+      <c r="G139" s="1">
+        <v>4</v>
+      </c>
+      <c r="H139" s="1">
+        <v>10</v>
+      </c>
+      <c r="I139" s="1">
+        <v>4</v>
+      </c>
+      <c r="J139" s="1"/>
+      <c r="K139" s="1"/>
+      <c r="L139" s="1"/>
+      <c r="M139" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N139" s="1"/>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>13</v>
+      </c>
+      <c r="B140" t="s">
+        <v>77</v>
+      </c>
+      <c r="C140" s="1">
+        <v>6</v>
+      </c>
+      <c r="D140" t="s">
+        <v>35</v>
+      </c>
+      <c r="E140" t="s">
+        <v>39</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G140" s="1">
+        <v>4</v>
+      </c>
+      <c r="H140" s="1">
+        <v>2</v>
+      </c>
+      <c r="J140" s="1"/>
+      <c r="K140" s="1"/>
+      <c r="L140" s="1"/>
+      <c r="M140" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N140" s="1"/>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>13</v>
+      </c>
+      <c r="B141" t="s">
+        <v>77</v>
+      </c>
+      <c r="C141" s="1">
+        <v>7</v>
+      </c>
+      <c r="D141" t="s">
+        <v>78</v>
+      </c>
+      <c r="E141" t="s">
+        <v>42</v>
+      </c>
+      <c r="F141" s="1">
+        <v>0</v>
+      </c>
+      <c r="G141" s="1">
+        <v>4</v>
+      </c>
+      <c r="H141" s="1">
+        <v>5</v>
+      </c>
+      <c r="I141" s="1">
+        <v>52</v>
+      </c>
+      <c r="J141" s="1"/>
+      <c r="K141" s="1"/>
+      <c r="L141" s="1"/>
+      <c r="M141" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N141" s="1"/>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>13</v>
+      </c>
+      <c r="B142" t="s">
+        <v>77</v>
+      </c>
+      <c r="C142" s="1">
+        <v>8</v>
+      </c>
+      <c r="D142" t="s">
+        <v>79</v>
+      </c>
+      <c r="E142" t="s">
+        <v>42</v>
+      </c>
+      <c r="F142" s="1">
+        <v>0</v>
+      </c>
+      <c r="G142" s="1">
+        <v>4</v>
+      </c>
+      <c r="H142" s="1">
+        <v>5</v>
+      </c>
+      <c r="I142" s="1">
+        <v>52</v>
+      </c>
+      <c r="J142" s="1"/>
+      <c r="K142" s="1"/>
+      <c r="L142" s="1"/>
+      <c r="M142" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N142" s="1"/>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>13</v>
+      </c>
+      <c r="B143" t="s">
+        <v>77</v>
+      </c>
+      <c r="C143" s="1">
+        <v>9</v>
+      </c>
+      <c r="D143" t="s">
+        <v>17</v>
+      </c>
+      <c r="E143" t="s">
+        <v>43</v>
+      </c>
+      <c r="H143" s="1">
+        <v>1</v>
+      </c>
+      <c r="I143" s="1">
+        <v>90</v>
+      </c>
+      <c r="J143" s="1">
+        <v>70</v>
+      </c>
+      <c r="K143" s="1">
+        <v>90</v>
+      </c>
+      <c r="L143" s="1">
+        <v>1</v>
+      </c>
+      <c r="M143" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N143" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>13</v>
+      </c>
+      <c r="B144" t="s">
+        <v>77</v>
+      </c>
+      <c r="C144" s="1">
+        <v>10</v>
+      </c>
+      <c r="D144" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" t="s">
+        <v>39</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G144" s="1">
+        <v>4</v>
+      </c>
+      <c r="H144" s="1">
+        <v>1</v>
+      </c>
+      <c r="J144" s="1"/>
+      <c r="K144" s="1"/>
+      <c r="L144" s="1"/>
+      <c r="M144" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N144" s="1"/>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>14</v>
+      </c>
+      <c r="B145" t="s">
+        <v>80</v>
+      </c>
+      <c r="C145" s="1">
+        <v>1</v>
+      </c>
+      <c r="D145" t="s">
+        <v>6</v>
+      </c>
+      <c r="E145" t="s">
+        <v>39</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G145" s="1">
+        <v>4</v>
+      </c>
+      <c r="H145" s="1">
+        <v>1</v>
+      </c>
+      <c r="J145" s="1"/>
+      <c r="K145" s="1"/>
+      <c r="L145" s="1"/>
+      <c r="M145" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N145" s="1"/>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>14</v>
+      </c>
+      <c r="B146" t="s">
+        <v>80</v>
+      </c>
+      <c r="C146" s="1">
+        <v>2</v>
+      </c>
+      <c r="D146" t="s">
+        <v>7</v>
+      </c>
+      <c r="E146" t="s">
+        <v>42</v>
+      </c>
+      <c r="F146" s="1">
+        <v>0</v>
+      </c>
+      <c r="G146" s="1">
+        <v>4</v>
+      </c>
+      <c r="H146" s="1">
+        <v>10</v>
+      </c>
+      <c r="I146" s="1">
+        <v>4</v>
+      </c>
+      <c r="J146" s="1"/>
+      <c r="K146" s="1"/>
+      <c r="L146" s="1"/>
+      <c r="M146" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N146" s="1"/>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>14</v>
+      </c>
+      <c r="B147" t="s">
+        <v>80</v>
+      </c>
+      <c r="C147" s="1">
+        <v>3</v>
+      </c>
+      <c r="D147" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" t="s">
+        <v>42</v>
+      </c>
+      <c r="F147" s="1">
+        <v>0</v>
+      </c>
+      <c r="G147" s="1">
+        <v>4</v>
+      </c>
+      <c r="H147" s="1">
+        <v>5</v>
+      </c>
+      <c r="I147" s="1">
+        <v>4</v>
+      </c>
+      <c r="J147" s="1"/>
+      <c r="K147" s="1"/>
+      <c r="L147" s="1"/>
+      <c r="M147" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N147" s="1"/>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>14</v>
+      </c>
+      <c r="B148" t="s">
+        <v>80</v>
+      </c>
+      <c r="C148" s="1">
+        <v>4</v>
+      </c>
+      <c r="D148" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148" t="s">
+        <v>42</v>
+      </c>
+      <c r="F148" s="1">
+        <v>0</v>
+      </c>
+      <c r="G148" s="1">
+        <v>4</v>
+      </c>
+      <c r="H148" s="1">
+        <v>5</v>
+      </c>
+      <c r="I148" s="1">
+        <v>4</v>
+      </c>
+      <c r="J148" s="1"/>
+      <c r="K148" s="1"/>
+      <c r="L148" s="1"/>
+      <c r="M148" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N148" s="1"/>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>14</v>
+      </c>
+      <c r="B149" t="s">
+        <v>80</v>
+      </c>
+      <c r="C149" s="1">
+        <v>5</v>
+      </c>
+      <c r="D149" t="s">
+        <v>10</v>
+      </c>
+      <c r="E149" t="s">
+        <v>42</v>
+      </c>
+      <c r="F149" s="1">
+        <v>0</v>
+      </c>
+      <c r="G149" s="1">
+        <v>4</v>
+      </c>
+      <c r="H149" s="1">
+        <v>10</v>
+      </c>
+      <c r="I149" s="1">
+        <v>4</v>
+      </c>
+      <c r="J149" s="1"/>
+      <c r="K149" s="1"/>
+      <c r="L149" s="1"/>
+      <c r="M149" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N149" s="1"/>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>14</v>
+      </c>
+      <c r="B150" t="s">
+        <v>80</v>
+      </c>
+      <c r="C150" s="1">
+        <v>6</v>
+      </c>
+      <c r="D150" t="s">
+        <v>35</v>
+      </c>
+      <c r="E150" t="s">
+        <v>39</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G150" s="1">
+        <v>4</v>
+      </c>
+      <c r="H150" s="1">
+        <v>2</v>
+      </c>
+      <c r="J150" s="1"/>
+      <c r="K150" s="1"/>
+      <c r="L150" s="1"/>
+      <c r="M150" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N150" s="1"/>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>14</v>
+      </c>
+      <c r="B151" t="s">
+        <v>80</v>
+      </c>
+      <c r="C151" s="1">
+        <v>7</v>
+      </c>
+      <c r="D151" t="s">
+        <v>81</v>
+      </c>
+      <c r="E151" t="s">
+        <v>39</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G151" s="1">
+        <v>4</v>
+      </c>
+      <c r="H151" s="1">
+        <v>5</v>
+      </c>
+      <c r="J151" s="1"/>
+      <c r="K151" s="1"/>
+      <c r="L151" s="1"/>
+      <c r="M151" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N151" s="1"/>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>14</v>
+      </c>
+      <c r="B152" t="s">
+        <v>80</v>
+      </c>
+      <c r="C152" s="1">
+        <v>8</v>
+      </c>
+      <c r="D152" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" t="s">
+        <v>39</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G152" s="1">
+        <v>4</v>
+      </c>
+      <c r="H152" s="1">
+        <v>1</v>
+      </c>
+      <c r="J152" s="1"/>
+      <c r="K152" s="1"/>
+      <c r="L152" s="1"/>
+      <c r="M152" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N152" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <tableParts count="1">
